--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -1124,18 +1124,18 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>23.75%</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>6449837</v>
+        <v>7409975</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>23540</v>
+        <v>27044</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1186,18 +1186,18 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>6449173</v>
+        <v>7433505</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>23710</v>
+        <v>27329</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>180天現金付款計劃</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1248,18 +1248,18 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>25.25%</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>5139693</v>
+        <v>5788640</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>25072</v>
+        <v>28237</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1310,18 +1310,18 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>6963540</v>
+        <v>8036872</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>23848</v>
+        <v>27524</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>180天現金付款計劃</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1372,18 +1372,18 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>25.25%</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>7619940</v>
+        <v>8582048</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>24038</v>
+        <v>27073</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1434,18 +1434,18 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>6396077</v>
+        <v>7275935</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>23343</v>
+        <v>26555</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1496,18 +1496,18 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>6395413</v>
+        <v>7275180</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>23513</v>
+        <v>26747</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>180天現金付款計劃</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1558,18 +1558,18 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>5026200</v>
+        <v>5641885</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>24518</v>
+        <v>27521</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1620,18 +1620,18 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>24.15%</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>6905798</v>
+        <v>7892192</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>23650</v>
+        <v>27028</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>180天現金付款計劃</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -1682,18 +1682,18 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>26.25%</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>7557552</v>
+        <v>8397912</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>23841</v>
+        <v>26492</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -1744,18 +1744,18 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>6346299</v>
+        <v>7123690</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>23162</v>
+        <v>25999</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -1868,18 +1868,18 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>4914698</v>
+        <v>5553750</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>23974</v>
+        <v>27091</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -1992,18 +1992,18 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>7504456</v>
+        <v>8254110</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>23673</v>
+        <v>26038</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2302,18 +2302,18 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>27.25%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>7454678</v>
+        <v>8171280</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>23516</v>
+        <v>25777</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -2612,18 +2612,18 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>7406892</v>
+        <v>8091000</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>23366</v>
+        <v>25524</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -2922,18 +2922,18 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>27.25%</t>
         </is>
       </c>
       <c r="K37" s="5" t="n">
-        <v>7294063</v>
+        <v>7995225</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>23010</v>
+        <v>25222</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -7519,44 +7519,44 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 317呎 (1房)
 $1139万
 $35,921/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 292呎 (1房)
 $1040万
 $35,634/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>C | 205呎 (开放式)
 $757万
 $36,941/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D | 272呎 (1房)
 $964万
 $35,426/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F7" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>E | 274呎 (1房)
 $964万
 $35,172/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -1480,34 +1480,34 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>9636000</v>
+        <v>7276000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>35426</v>
+        <v>26750</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>7275180</v>
+        <v>7276000</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>26747</v>
+        <v>26750</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>180天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7543,12 +7543,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 272呎 (1房)
-$964万
-$35,426/呎
-(在售)</t>
+$728万
+$26,750/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1170,34 +1170,34 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>9717000</v>
+        <v>7434000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>35724</v>
+        <v>27331</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>7433505</v>
+        <v>7434000</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>27329</v>
+        <v>27331</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>180天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -7363,17 +7363,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7480,36 +7480,36 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 292呎 (1房)
 $1049万
 $35,932/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>C | 205呎 (开放式)
 $774万
 $37,776/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E6" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 272呎 (1房)
-$972万
-$35,724/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F6" s="22" t="inlineStr">
+$743万
+$27,331/呎
+(26年-09月-20日)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>E | 274呎 (1房)
 $972万
 $35,467/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -7501,7 +7501,7 @@
           <t>D | 272呎 (1房)
 $743万
 $27,331/呎
-(26年-09月-20日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -7548,7 +7548,7 @@
           <t>D | 272呎 (1房)
 $728万
 $26,750/呎
-(26年-09月-11日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>7343700</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>26999</v>
+        <v>26900</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>7343700</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>26999</v>
+        <v>26900</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>7219000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>35044</v>
+        <v>35215</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>5504488</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>26721</v>
+        <v>26851</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>4840000</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>23495</v>
+        <v>23610</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>4840000</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>23495</v>
+        <v>23610</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>4790000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>23252</v>
+        <v>23366</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>4790000</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>23252</v>
+        <v>23366</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>4341000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>21073</v>
+        <v>21176</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>4341000</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>21073</v>
+        <v>21176</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>4375000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>21238</v>
+        <v>21341</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>4375000</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>21238</v>
+        <v>21341</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>6461000</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>20446</v>
+        <v>20382</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>6461000</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>20446</v>
+        <v>20382</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>4251000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>20636</v>
+        <v>20737</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>4251000</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>20636</v>
+        <v>20737</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>6391000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>20225</v>
+        <v>20161</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>6391000</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>20225</v>
+        <v>20161</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>4208000</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>20427</v>
+        <v>20527</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>4208000</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>20427</v>
+        <v>20527</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>6354000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>20108</v>
+        <v>20044</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>6354000</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>20108</v>
+        <v>20044</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>4034000</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>19583</v>
+        <v>19678</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>4034000</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>19583</v>
+        <v>19678</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>6435000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>20364</v>
+        <v>20300</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>6435000</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>20364</v>
+        <v>20300</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>6271000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>19845</v>
+        <v>19782</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>6271000</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>19845</v>
+        <v>19782</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>6342000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>20070</v>
+        <v>20006</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>6342000</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>20070</v>
+        <v>20006</v>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>6258000</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>19804</v>
+        <v>19741</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>6258000</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>19804</v>
+        <v>19741</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>6157000</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>19484</v>
+        <v>19423</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>6157000</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>19484</v>
+        <v>19423</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>6168000</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>19519</v>
+        <v>19457</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>6168000</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>19519</v>
+        <v>19457</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>6300000</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>26809</v>
+        <v>26923</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>6300000</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>26809</v>
+        <v>26923</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
@@ -7451,9 +7451,9 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>D | 272呎 (1房)
+          <t>D | 273呎 (1房)
 $734万
-$26,999/呎
+$26,900/呎
 (24年-11月-29日)</t>
         </is>
       </c>
@@ -7678,9 +7678,9 @@
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>C | 206呎 (开放式)
+          <t>C | 205呎 (开放式)
 $722万
-$35,044/呎
+$35,215/呎
 (在售)</t>
         </is>
       </c>
@@ -7725,9 +7725,9 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>C | 206呎 (开放式)
+          <t>C | 205呎 (开放式)
 $484万
-$23,495/呎
+$23,610/呎
 (26年-05月-04日)</t>
         </is>
       </c>
@@ -7772,9 +7772,9 @@
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>C | 206呎 (开放式)
+          <t>C | 205呎 (开放式)
 $479万
-$23,252/呎
+$23,366/呎
 (26年-04月-22日)</t>
         </is>
       </c>
@@ -7819,9 +7819,9 @@
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>C | 206呎 (开放式)
+          <t>C | 205呎 (开放式)
 $434万
-$21,073/呎
+$21,176/呎
 (25年-08月-29日)</t>
         </is>
       </c>
@@ -7850,9 +7850,9 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>A | 316呎 (1房)
+          <t>A | 317呎 (1房)
 $646万
-$20,446/呎
+$20,382/呎
 (26年-03月-27日)</t>
         </is>
       </c>
@@ -7866,9 +7866,9 @@
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>C | 206呎 (开放式)
+          <t>C | 205呎 (开放式)
 $438万
-$21,238/呎
+$21,341/呎
 (25年-07月-15日)</t>
         </is>
       </c>
@@ -7897,9 +7897,9 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>A | 316呎 (1房)
+          <t>A | 317呎 (1房)
 $639万
-$20,225/呎
+$20,161/呎
 (26年-04月-16日)</t>
         </is>
       </c>
@@ -7913,9 +7913,9 @@
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>C | 206呎 (开放式)
+          <t>C | 205呎 (开放式)
 $425万
-$20,636/呎
+$20,737/呎
 (25年-07月-02日)</t>
         </is>
       </c>
@@ -7944,9 +7944,9 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>A | 316呎 (1房)
+          <t>A | 317呎 (1房)
 $635万
-$20,108/呎
+$20,044/呎
 (26年-03月-06日)</t>
         </is>
       </c>
@@ -7960,9 +7960,9 @@
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>C | 206呎 (开放式)
+          <t>C | 205呎 (开放式)
 $421万
-$20,427/呎
+$20,527/呎
 (25年-06月-10日)</t>
         </is>
       </c>
@@ -7991,9 +7991,9 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>A | 316呎 (1房)
+          <t>A | 317呎 (1房)
 $644万
-$20,364/呎
+$20,300/呎
 (25年-03月-21日)</t>
         </is>
       </c>
@@ -8007,9 +8007,9 @@
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>C | 206呎 (开放式)
+          <t>C | 205呎 (开放式)
 $403万
-$19,583/呎
+$19,678/呎
 (24年-06月-03日)</t>
         </is>
       </c>
@@ -8038,9 +8038,9 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>A | 316呎 (1房)
+          <t>A | 317呎 (1房)
 $627万
-$19,845/呎
+$19,782/呎
 (26年-04月-23日)</t>
         </is>
       </c>
@@ -8085,9 +8085,9 @@
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>A | 316呎 (1房)
+          <t>A | 317呎 (1房)
 $634万
-$20,070/呎
+$20,006/呎
 (25年-06月-13日)</t>
         </is>
       </c>
@@ -8179,9 +8179,9 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>A | 316呎 (1房)
+          <t>A | 317呎 (1房)
 $626万
-$19,804/呎
+$19,741/呎
 (25年-07月-02日)</t>
         </is>
       </c>
@@ -8273,9 +8273,9 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>A | 316呎 (1房)
+          <t>A | 317呎 (1房)
 $616万
-$19,484/呎
+$19,423/呎
 (25年-08月-04日)</t>
         </is>
       </c>
@@ -8320,9 +8320,9 @@
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>A | 316呎 (1房)
+          <t>A | 317呎 (1房)
 $617万
-$19,519/呎
+$19,457/呎
 (25年-08月-29日)</t>
         </is>
       </c>
@@ -8391,9 +8391,9 @@
       </c>
       <c r="E25" s="21" t="inlineStr">
         <is>
-          <t>D | 235呎 (1房)
+          <t>D | 234呎 (1房)
 $630万
-$26,809/呎
+$26,923/呎
 (26年-05月-21日)</t>
         </is>
       </c>
